--- a/AAII_Financials/Quarterly/JAPAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAPAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>JAPAY</t>
   </si>
@@ -656,101 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -787,32 +791,35 @@
       <c r="N8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P8" s="3">
         <v>4609900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4732200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4619100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3861200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3838700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4481300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4389200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4023100</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -849,32 +856,35 @@
       <c r="N9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" s="3">
         <v>2020000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1905200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1864200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1535700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1705200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1825800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1755300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1592000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -911,32 +921,35 @@
       <c r="N10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="3">
         <v>2589900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2827000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2754900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2325500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2133500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2655500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2633900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2431100</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -997,32 +1011,35 @@
       <c r="N12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="3">
         <v>153300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>106100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>114900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>103200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>125400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>109500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>124100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,32 +1141,35 @@
       <c r="N14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" s="3">
         <v>64800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>106900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>93900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>16200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1183,32 +1206,35 @@
       <c r="N15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P15" s="3">
         <v>187000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>205400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>198100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>174800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>184000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>204900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>202900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>192300</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,8 +1254,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1266,32 +1293,35 @@
       <c r="N17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P17" s="3">
         <v>4082900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3479300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3240000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2676800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3712800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3337700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3198900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2846200</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1328,32 +1358,35 @@
       <c r="N18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P18" s="3">
         <v>527100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1252800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1379000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1184400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>125900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1143600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1190400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1176900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1376,8 +1409,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1414,32 +1448,35 @@
       <c r="N20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P20" s="3">
         <v>-66300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-69800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>16100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-38600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-21500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1476,32 +1513,35 @@
       <c r="N21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P21" s="3">
         <v>801300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1500500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1650700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1508400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>412300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1468400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1547400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1520800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1538,32 +1578,35 @@
       <c r="N22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P22" s="3">
         <v>50000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>53600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>40500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>28400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>42600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>43100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>42300</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1600,32 +1643,35 @@
       <c r="N23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P23" s="3">
         <v>410800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1114000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1255600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1160000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>58900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1079500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1159500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1149100</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1662,32 +1708,35 @@
       <c r="N24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P24" s="3">
         <v>125000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>227700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>309300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>332600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>59600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>255100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>337000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>310900</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1748,8 +1797,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -1786,32 +1838,35 @@
       <c r="N26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P26" s="3">
         <v>285700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>886300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>946300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>827400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>824400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>822500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>838200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -1848,32 +1903,35 @@
       <c r="N27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P27" s="3">
         <v>276300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>891600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>943300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>824100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>819200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>818800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>836300</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1972,8 +2033,8 @@
       <c r="N29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2120,8 +2187,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -2158,32 +2228,35 @@
       <c r="N32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P32" s="3">
         <v>66300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>101000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>69800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-16100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>38600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>21500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-14500</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -2220,32 +2293,35 @@
       <c r="N33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P33" s="3">
         <v>276300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>891600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>943300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>824100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>819200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>818800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>836300</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2306,8 +2382,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2344,99 +2423,105 @@
       <c r="N35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P35" s="3">
         <v>276300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>891600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>943300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>824100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>819200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>818800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>836300</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2483,70 +2569,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5093400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5301000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5996700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6898400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6762400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5070600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7379300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5818400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5721300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5818400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5721300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5003600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6154900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4966600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5046200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4350900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4958300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4547000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3533200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3118600</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -2584,465 +2674,489 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>267500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>375000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>253300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>233900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>118500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>131700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>151300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>156300</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>4637200</v>
+      </c>
+      <c r="E43" s="3">
         <v>4086300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4028200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3619000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4089800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3776800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3952200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3816700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3885700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3816700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3885700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3564400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3388400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3496400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3730900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2957200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3136800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3505100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3414700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3169900</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>6882700</v>
+      </c>
+      <c r="E44" s="3">
         <v>6761600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6672200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6088800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5853100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5788000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5906600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5536500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5341500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5536500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5341500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5304600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4912500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4371800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4412500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3874000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3869100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3894900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4041200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4064800</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>7091600</v>
+      </c>
+      <c r="E45" s="3">
         <v>7520600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7169900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6149000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4811900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5098200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5737600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4800600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5133300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4800600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5133300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4886500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4614200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3548500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3999100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3494300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3864600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3569000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3994800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3682100</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>23704900</v>
+      </c>
+      <c r="E46" s="3">
         <v>23669500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23866900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22755200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21517300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19733600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23123700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19972200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20081800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19972200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20081800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18759100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19337500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16758300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17441900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14910400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15947300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15647600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15135100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14191700</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>1752700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1601300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2072800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1915500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1866900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2027200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2044800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1936100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1995300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1936100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1995300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2020000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1400900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1349000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1362200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1012900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1033100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1075600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1085400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1142300</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>6121200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6249200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6253400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5773400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5533500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5594900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5827800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5441700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5603300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5441700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5603300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5836100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5576700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5205500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5652400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5080100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5226900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5494200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5639300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5669400</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>20744400</v>
+      </c>
+      <c r="E49" s="3">
         <v>21167100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23851900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21630300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19387000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19340500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20029700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19658400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19999300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19658400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19999300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20441900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19116800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18498700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19153500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15934400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16269000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17028200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17449300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>17281700</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3165,70 +3282,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>91</v>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>91</v>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P52" s="3">
         <v>1059500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1114200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1203400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1224700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1192600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1345700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1401800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1391600</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3289,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>53338800</v>
+      </c>
+      <c r="E54" s="3">
         <v>53698200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>57270700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53242200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48914400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47330700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51660000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47545600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>48237100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47545600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48237100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>47742700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>46491400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42925800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44813300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38162400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39668800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>40591300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>40710800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>39676700</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3399,380 +3529,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3836000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4539400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3934900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4194800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3262200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3459200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4205400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3255700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3332700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3255700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3332700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3560400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1938500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2907100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3116700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3212400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2909900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3072300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2856700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2813800</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>720300</v>
+      </c>
+      <c r="E58" s="3">
         <v>507900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1292500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1136400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>475800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>531000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1655300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>942400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>942400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1069000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>974900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1071000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1085600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1079100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>981700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1205100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>579400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1163700</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>7039500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7243700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7646200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8335000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7042700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6785000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7811600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6810300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6299300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6810300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6299300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6084600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8181500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5450500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5575900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4860400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6415600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5369100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5392100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5103800</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>11595800</v>
+      </c>
+      <c r="E60" s="3">
         <v>12291000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12873600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13666200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10780700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10775200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13672300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10466700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10574400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10466700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10574400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10714000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11094900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9428500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9778300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9151900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10307200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9646500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8828200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9081200</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>9595400</v>
+      </c>
+      <c r="E61" s="3">
         <v>10198900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9980600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9846800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6688400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6209800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6448000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6388000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6548100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6388000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6548100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6265300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5829100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4926400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5670400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5311700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5329200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5767200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6233900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6181200</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>2498600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2518600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2931600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2694200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1353700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1315100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1513700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1792400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1717800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1792400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1717800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1673800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3888300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3906400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4058500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3890800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4205000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4509900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4606900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4530500</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3957,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>26127600</v>
+      </c>
+      <c r="E66" s="3">
         <v>27450100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28562900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28762300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20783600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20406200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23904400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20754000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20919400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20754000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20919400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20765000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21354300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18749500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20029400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18867700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20369200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20475100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20233100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20356400</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -4291,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>21001000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20496200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22073300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19316300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>20746900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20971600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22646700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21190900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21974900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21190900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21974900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22825100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21945500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19414400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20446900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19089300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19682900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20788800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>21204500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>20388000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4539,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>27032300</v>
+      </c>
+      <c r="E76" s="3">
         <v>26066600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28137600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23957700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27608100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26376000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27171500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26238800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26750000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26238800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26750000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26383700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25137100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24176300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24783900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19294700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19299600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20116200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20477800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19320300</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4663,75 +4852,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -4768,32 +4963,35 @@
       <c r="N81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P81" s="3">
         <v>276300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>891600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>943300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>824100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>819200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>818800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>836300</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E83" s="3">
         <v>290700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>350500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>294000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>305000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>317700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>363700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>377700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>372900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>377700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>372900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>381900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>340500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>348700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>341500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>307900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>325000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>346300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>344800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>329300</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1794800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1448200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1206200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1513800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1233200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>408800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>543300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1898600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1045700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1898600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1045700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>418700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>995200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1489300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>479900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>258800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1167700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1831800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1194500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>90800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-179600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-311000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-176200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-264300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-185800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-175100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-237300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-149900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-116100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-149900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-116100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-167300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-34686000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-24097000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21003000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19622000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-30403000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25631000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-142600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-139500</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-282600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-597700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-352600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1889900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-183000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-156700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-421500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-421500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-313700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-226100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-198700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-150900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-188200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-170500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-176500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-165000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5546,70 +5779,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E96" s="3">
         <v>2500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>34000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>29500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1141900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1114600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>34800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>91</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-847400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-25700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-858200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-829400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-35000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-968900</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5794,190 +6037,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-728600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-351800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2191300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>458500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2256100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1016200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1676800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>228900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1676800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>228900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1477400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>363400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1271000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-278900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-775300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-424600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-567100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-626500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-936800</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>309500</v>
+      </c>
+      <c r="E101" s="3">
         <v>223700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-188500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>67500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>267800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-145100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-539100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>184400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>586700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>184400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>586700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>280300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-504800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>170200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>537400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>226000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>70800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-13100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>23000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>169100</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>803300</v>
+      </c>
+      <c r="E102" s="3">
         <v>634500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>531300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1842800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1994800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1806600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1214200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>280000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1120900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>280000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1120900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1517500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>627800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>189900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>629800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-441400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>625700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1081100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>414500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-841900</v>
       </c>
     </row>
